--- a/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
+++ b/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917728E2-E788-4D7F-9C7E-C00EBB8672F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC368F6-77AE-42F9-A1EB-9CEBCFBC4D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -343,15 +343,6 @@
     <t xml:space="preserve">COMISION POR CUENTA </t>
   </si>
   <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>CUIT DEL EDIFICIO: 30-66055743-8 - PERÍODO:  agosto - HORARIOS DE ATENCION: LUNES A VIERNES 10 A 15HS</t>
-  </si>
-  <si>
-    <t>Seguro de vida Sra. Silvana - La Holando - Mes de julio</t>
-  </si>
-  <si>
     <t>Gasto particular: Reliquidacion de deuda UF 9 y 26</t>
   </si>
   <si>
@@ -370,9 +361,6 @@
     <t>Transf 03/08</t>
   </si>
   <si>
-    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 -EN JULIO SE ABONAR PARTE DE LA MISMA -  LA DEUDA DESCIENDE A $1.581.282,36 - EN AGOSTO SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) - LA DEUDA AL FINALIZAR AGOSTO SE UBICA EN: $1.181.282,36</t>
-  </si>
-  <si>
     <t>Debito 05/08</t>
   </si>
   <si>
@@ -380,6 +368,18 @@
   </si>
   <si>
     <t>Uf 13 deposito $500.000</t>
+  </si>
+  <si>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>CUIT DEL EDIFICIO: 30-66055743-8 - PERÍODO:  SEPTIEMBRE - HORARIOS DE ATENCION: LUNES A VIERNES 10 A 15HS</t>
+  </si>
+  <si>
+    <t>Seguro de vida Sra. Silvana - La Holando - Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 -EN AGOSTO SE ABONAR PARTE DE LA MISMA -  LA DEUDA DESCIENDE A $1.581.282,36 - EN SEPTIEMBRE SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) - LA DEUDA AL FINALIZAR SEPTIEMBRE SE UBICA EN: $1.181.282,36</t>
   </si>
 </sst>
 </file>
@@ -1252,6 +1252,7 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1306,12 +1307,48 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1342,43 +1379,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="17"/>
@@ -1814,49 +1814,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="175" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="175"/>
+      <c r="B8" s="176" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="176"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="175"/>
-      <c r="C9" s="175"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="175"/>
-      <c r="C10" s="175"/>
+      <c r="B10" s="176"/>
+      <c r="C10" s="176"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="183" t="s">
+      <c r="A13" s="184" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="183"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="183"/>
+      <c r="B13" s="184"/>
+      <c r="C13" s="184"/>
+      <c r="D13" s="184"/>
+      <c r="E13" s="184"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="183"/>
-      <c r="B14" s="183"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="183"/>
+      <c r="A14" s="184"/>
+      <c r="B14" s="184"/>
+      <c r="C14" s="184"/>
+      <c r="D14" s="184"/>
+      <c r="E14" s="184"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="183"/>
-      <c r="B15" s="183"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
+      <c r="A15" s="184"/>
+      <c r="B15" s="184"/>
+      <c r="C15" s="184"/>
+      <c r="D15" s="184"/>
+      <c r="E15" s="184"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="183"/>
-      <c r="B16" s="183"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
+      <c r="A16" s="184"/>
+      <c r="B16" s="184"/>
+      <c r="C16" s="184"/>
+      <c r="D16" s="184"/>
+      <c r="E16" s="184"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -1883,16 +1883,16 @@
       <c r="G21" s="22"/>
     </row>
     <row r="22" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="176" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="177"/>
+      <c r="A22" s="177" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="178"/>
       <c r="C22" s="5"/>
       <c r="D22" s="172">
         <v>400000</v>
       </c>
       <c r="E22" s="121" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F22" s="48"/>
       <c r="H22" s="22"/>
@@ -1919,23 +1919,23 @@
       <c r="E24" s="106"/>
     </row>
     <row r="25" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="176" t="s">
+      <c r="A25" s="177" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="177"/>
+      <c r="B25" s="178"/>
       <c r="C25" s="133"/>
       <c r="D25" s="174">
         <v>149073.01</v>
       </c>
       <c r="E25" s="121" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="176" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="177"/>
+      <c r="A26" s="177" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="178"/>
       <c r="C26" s="133"/>
       <c r="D26" s="168">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>750368</v>
       </c>
       <c r="E30" s="121" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
@@ -2154,22 +2154,22 @@
       <c r="E48" s="117"/>
     </row>
     <row r="49" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="176"/>
-      <c r="B49" s="177"/>
+      <c r="A49" s="177"/>
+      <c r="B49" s="178"/>
       <c r="C49" s="5"/>
       <c r="D49" s="103"/>
       <c r="E49" s="101"/>
     </row>
     <row r="50" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="176"/>
-      <c r="B50" s="177"/>
+      <c r="A50" s="177"/>
+      <c r="B50" s="178"/>
       <c r="C50" s="5"/>
       <c r="D50" s="103"/>
       <c r="E50" s="101"/>
     </row>
     <row r="51" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="181"/>
-      <c r="B51" s="182"/>
+      <c r="A51" s="182"/>
+      <c r="B51" s="183"/>
       <c r="C51" s="5"/>
       <c r="D51" s="103"/>
       <c r="E51" s="101"/>
@@ -2254,51 +2254,51 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="180" t="s">
+      <c r="A66" s="181" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="180"/>
-      <c r="C66" s="180"/>
-      <c r="D66" s="180"/>
-      <c r="E66" s="180"/>
+      <c r="B66" s="181"/>
+      <c r="C66" s="181"/>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="180"/>
-      <c r="B67" s="180"/>
-      <c r="C67" s="180"/>
-      <c r="D67" s="180"/>
-      <c r="E67" s="180"/>
+      <c r="A67" s="181"/>
+      <c r="B67" s="181"/>
+      <c r="C67" s="181"/>
+      <c r="D67" s="181"/>
+      <c r="E67" s="181"/>
     </row>
     <row r="68" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="180"/>
-      <c r="B68" s="180"/>
-      <c r="C68" s="180"/>
-      <c r="D68" s="180"/>
-      <c r="E68" s="180"/>
+      <c r="A68" s="181"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="181"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
     </row>
     <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="184" t="s">
-        <v>112</v>
-      </c>
-      <c r="B70" s="185"/>
-      <c r="C70" s="185"/>
-      <c r="D70" s="185"/>
-      <c r="E70" s="186"/>
+      <c r="A70" s="185" t="s">
+        <v>115</v>
+      </c>
+      <c r="B70" s="186"/>
+      <c r="C70" s="186"/>
+      <c r="D70" s="186"/>
+      <c r="E70" s="187"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="187"/>
-      <c r="B71" s="188"/>
-      <c r="C71" s="188"/>
-      <c r="D71" s="188"/>
-      <c r="E71" s="189"/>
+      <c r="A71" s="188"/>
+      <c r="B71" s="189"/>
+      <c r="C71" s="189"/>
+      <c r="D71" s="189"/>
+      <c r="E71" s="190"/>
     </row>
     <row r="72" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="190"/>
-      <c r="B72" s="191"/>
-      <c r="C72" s="191"/>
-      <c r="D72" s="191"/>
-      <c r="E72" s="192"/>
+      <c r="A72" s="191"/>
+      <c r="B72" s="192"/>
+      <c r="C72" s="192"/>
+      <c r="D72" s="192"/>
+      <c r="E72" s="193"/>
     </row>
     <row r="73" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="163"/>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="78" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B78" s="169">
         <v>-99000</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B79" s="169">
         <v>-270000</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="80" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B80" s="169">
         <v>-86980</v>
@@ -2491,16 +2491,16 @@
     <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A97" s="179" t="s">
+      <c r="A97" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="B97" s="179"/>
-      <c r="C97" s="179"/>
+      <c r="B97" s="180"/>
+      <c r="C97" s="180"/>
     </row>
     <row r="98" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="179"/>
-      <c r="B98" s="179"/>
-      <c r="C98" s="179"/>
+      <c r="A98" s="180"/>
+      <c r="B98" s="180"/>
+      <c r="C98" s="180"/>
     </row>
     <row r="99" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="118"/>
@@ -2523,32 +2523,32 @@
       <c r="M101" s="8"/>
     </row>
     <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="178"/>
-      <c r="B102" s="178"/>
-      <c r="C102" s="178"/>
-      <c r="D102" s="178"/>
-      <c r="E102" s="178"/>
+      <c r="A102" s="179"/>
+      <c r="B102" s="179"/>
+      <c r="C102" s="179"/>
+      <c r="D102" s="179"/>
+      <c r="E102" s="179"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="178"/>
-      <c r="B103" s="178"/>
-      <c r="C103" s="178"/>
-      <c r="D103" s="178"/>
-      <c r="E103" s="178"/>
+      <c r="A103" s="179"/>
+      <c r="B103" s="179"/>
+      <c r="C103" s="179"/>
+      <c r="D103" s="179"/>
+      <c r="E103" s="179"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="178"/>
-      <c r="B104" s="178"/>
-      <c r="C104" s="178"/>
-      <c r="D104" s="178"/>
-      <c r="E104" s="178"/>
+      <c r="A104" s="179"/>
+      <c r="B104" s="179"/>
+      <c r="C104" s="179"/>
+      <c r="D104" s="179"/>
+      <c r="E104" s="179"/>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="178"/>
-      <c r="B105" s="178"/>
-      <c r="C105" s="178"/>
-      <c r="D105" s="178"/>
-      <c r="E105" s="178"/>
+      <c r="A105" s="179"/>
+      <c r="B105" s="179"/>
+      <c r="C105" s="179"/>
+      <c r="D105" s="179"/>
+      <c r="E105" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2598,12 +2598,12 @@
     <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="194" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2618,10 +2618,10 @@
     <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2636,10 +2636,10 @@
     <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2647,11 +2647,11 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="208">
+      <c r="L3" s="196">
         <f>Q3</f>
         <v>2402681.65</v>
       </c>
-      <c r="M3" s="208"/>
+      <c r="M3" s="196"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
@@ -2662,10 +2662,10 @@
     <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2673,97 +2673,97 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="209"/>
-      <c r="M4" s="209"/>
+      <c r="L4" s="197"/>
+      <c r="M4" s="197"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
     <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="212" t="s">
+      <c r="A5" s="202" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="213"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="213"/>
-      <c r="K5" s="213"/>
-      <c r="L5" s="213"/>
-      <c r="M5" s="213"/>
-      <c r="N5" s="213"/>
-      <c r="O5" s="214"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="203"/>
+      <c r="O5" s="204"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="210" t="s">
+      <c r="A6" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="194" t="s">
+      <c r="B6" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="194" t="s">
+      <c r="C6" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="194" t="s">
+      <c r="D6" s="200" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="194" t="s">
+      <c r="E6" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="194" t="s">
+      <c r="F6" s="200" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="194" t="s">
+      <c r="G6" s="200" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="203" t="s">
+      <c r="H6" s="216" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="203" t="s">
+      <c r="I6" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="198" t="s">
+      <c r="J6" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="211" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="201" t="s">
+      <c r="L6" s="214" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="196" t="s">
+      <c r="N6" s="209" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="215" t="s">
+      <c r="O6" s="205" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="211"/>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="199"/>
-      <c r="K7" s="200"/>
-      <c r="L7" s="202"/>
+      <c r="A7" s="199"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="212"/>
+      <c r="K7" s="213"/>
+      <c r="L7" s="215"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 17/09</v>
-      </c>
-      <c r="N7" s="197"/>
-      <c r="O7" s="216"/>
+        <v>VTO 16/10</v>
+      </c>
+      <c r="N7" s="210"/>
+      <c r="O7" s="206"/>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -3457,11 +3457,11 @@
       <c r="A20" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="217">
+      <c r="B20" s="175">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="C20" s="217" t="s">
+      <c r="C20" s="175" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="86"/>
@@ -4323,87 +4323,96 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="193" t="s">
+      <c r="C38" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="193"/>
-      <c r="E38" s="193"/>
-      <c r="F38" s="193"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="193"/>
-      <c r="K38" s="193"/>
-      <c r="L38" s="193"/>
-      <c r="M38" s="193"/>
+      <c r="D38" s="207"/>
+      <c r="E38" s="207"/>
+      <c r="F38" s="207"/>
+      <c r="G38" s="207"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="207"/>
+      <c r="J38" s="207"/>
+      <c r="K38" s="207"/>
+      <c r="L38" s="207"/>
+      <c r="M38" s="207"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="193"/>
-      <c r="D39" s="193"/>
-      <c r="E39" s="193"/>
-      <c r="F39" s="193"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
-      <c r="I39" s="193"/>
-      <c r="J39" s="193"/>
-      <c r="K39" s="193"/>
-      <c r="L39" s="193"/>
-      <c r="M39" s="193"/>
+      <c r="C39" s="207"/>
+      <c r="D39" s="207"/>
+      <c r="E39" s="207"/>
+      <c r="F39" s="207"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="207"/>
+      <c r="J39" s="207"/>
+      <c r="K39" s="207"/>
+      <c r="L39" s="207"/>
+      <c r="M39" s="207"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="193"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="193"/>
-      <c r="K40" s="193"/>
-      <c r="L40" s="193"/>
-      <c r="M40" s="193"/>
+      <c r="C40" s="207"/>
+      <c r="D40" s="207"/>
+      <c r="E40" s="207"/>
+      <c r="F40" s="207"/>
+      <c r="G40" s="207"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="207"/>
+      <c r="J40" s="207"/>
+      <c r="K40" s="207"/>
+      <c r="L40" s="207"/>
+      <c r="M40" s="207"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="193"/>
-      <c r="D41" s="193"/>
-      <c r="E41" s="193"/>
-      <c r="F41" s="193"/>
-      <c r="G41" s="193"/>
-      <c r="H41" s="193"/>
-      <c r="I41" s="193"/>
-      <c r="J41" s="193"/>
-      <c r="K41" s="193"/>
-      <c r="L41" s="193"/>
-      <c r="M41" s="193"/>
+      <c r="C41" s="207"/>
+      <c r="D41" s="207"/>
+      <c r="E41" s="207"/>
+      <c r="F41" s="207"/>
+      <c r="G41" s="207"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="207"/>
+      <c r="J41" s="207"/>
+      <c r="K41" s="207"/>
+      <c r="L41" s="207"/>
+      <c r="M41" s="207"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="193"/>
-      <c r="D42" s="193"/>
-      <c r="E42" s="193"/>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="193"/>
-      <c r="I42" s="193"/>
-      <c r="J42" s="193"/>
-      <c r="K42" s="193"/>
-      <c r="L42" s="193"/>
-      <c r="M42" s="193"/>
+      <c r="C42" s="207"/>
+      <c r="D42" s="207"/>
+      <c r="E42" s="207"/>
+      <c r="F42" s="207"/>
+      <c r="G42" s="207"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="207"/>
+      <c r="J42" s="207"/>
+      <c r="K42" s="207"/>
+      <c r="L42" s="207"/>
+      <c r="M42" s="207"/>
     </row>
     <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="193"/>
-      <c r="D43" s="193"/>
-      <c r="E43" s="193"/>
-      <c r="F43" s="193"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="193"/>
-      <c r="I43" s="193"/>
-      <c r="J43" s="193"/>
-      <c r="K43" s="193"/>
-      <c r="L43" s="193"/>
-      <c r="M43" s="193"/>
+      <c r="C43" s="207"/>
+      <c r="D43" s="207"/>
+      <c r="E43" s="207"/>
+      <c r="F43" s="207"/>
+      <c r="G43" s="207"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="207"/>
+      <c r="J43" s="207"/>
+      <c r="K43" s="207"/>
+      <c r="L43" s="207"/>
+      <c r="M43" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4414,15 +4423,6 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4436,7 +4436,7 @@
   <sheetData>
     <row r="6" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C6" s="171" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
+++ b/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC368F6-77AE-42F9-A1EB-9CEBCFBC4D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9385459-5F95-471C-9F7F-3EBA01AE04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="112">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -343,33 +348,9 @@
     <t xml:space="preserve">COMISION POR CUENTA </t>
   </si>
   <si>
-    <t>Gasto particular: Reliquidacion de deuda UF 9 y 26</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - leer cartel debajo</t>
-  </si>
-  <si>
-    <t>Deposito ya identificado 27/03</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados</t>
-  </si>
-  <si>
-    <t>Transf 03/08</t>
-  </si>
-  <si>
-    <t>Debito 05/08</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA - EDESUR</t>
   </si>
   <si>
-    <t>Uf 13 deposito $500.000</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -379,7 +360,19 @@
     <t>Seguro de vida Sra. Silvana - La Holando - Mes de AGOSTO</t>
   </si>
   <si>
-    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 -EN AGOSTO SE ABONAR PARTE DE LA MISMA -  LA DEUDA DESCIENDE A $1.581.282,36 - EN SEPTIEMBRE SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) - LA DEUDA AL FINALIZAR SEPTIEMBRE SE UBICA EN: $1.181.282,36</t>
+    <t>Debito 09/09</t>
+  </si>
+  <si>
+    <t>Transf 21/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 -EN EL MES 7 SE ABONAR PARTE DE LA MISMA -  LA DEUDA DESCIENDE A $1.581.282,36 - EN EL MES 8 SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) - EN EL MES 9 SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) -   LA DEUDA AL FINALIZAR SEPTIEMBRE SE UBICA EN: $781.282,36 </t>
+  </si>
+  <si>
+    <t>Honorarios administracion - leer cartel debajo - Deuda vieja</t>
+  </si>
+  <si>
+    <t>A la administracion se le debe en conepto de "deuda vieja" el monto especificado en el cartel de abajo - Por separado se adeudan honorarios del mes 7, 8 y 9 del 2026</t>
   </si>
 </sst>
 </file>
@@ -394,7 +387,7 @@
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,15 +567,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -655,12 +641,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="29">
     <border>
@@ -1008,7 +988,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1246,13 +1226,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1307,6 +1284,45 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1325,12 +1341,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1344,39 +1354,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1457,9 +1434,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1497,9 +1474,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1532,9 +1509,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1567,9 +1561,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1743,21 +1754,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="73" t="s">
         <v>84</v>
@@ -1766,7 +1777,7 @@
       <c r="D1" s="73"/>
       <c r="E1" s="74"/>
     </row>
-    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="75" t="s">
         <v>47</v>
@@ -1775,7 +1786,7 @@
       <c r="D2" s="75"/>
       <c r="E2" s="76"/>
     </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="93" t="s">
         <v>45</v>
@@ -1784,7 +1795,7 @@
       <c r="D3" s="93"/>
       <c r="E3" s="76"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1795,16 +1806,16 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="17"/>
       <c r="D5" s="75"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>82</v>
       </c>
@@ -1813,57 +1824,57 @@
       <c r="D6" s="20"/>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="176" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="176"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="184" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="173" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="173"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="173"/>
+      <c r="C10" s="173"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="181" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="184"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="184"/>
-      <c r="E13" s="184"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="184"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="184"/>
-      <c r="B15" s="184"/>
-      <c r="C15" s="184"/>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="184"/>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="181"/>
+      <c r="C13" s="181"/>
+      <c r="D13" s="181"/>
+      <c r="E13" s="181"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="181"/>
+      <c r="B14" s="181"/>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="181"/>
+      <c r="B15" s="181"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="181"/>
+      <c r="B16" s="181"/>
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1872,7 +1883,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>36</v>
       </c>
@@ -1882,13 +1893,13 @@
       <c r="E21" s="98"/>
       <c r="G21" s="22"/>
     </row>
-    <row r="22" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="177" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="178"/>
+    <row r="22" spans="1:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="174" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="175"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="172">
+      <c r="D22" s="171">
         <v>400000</v>
       </c>
       <c r="E22" s="121" t="s">
@@ -1897,105 +1908,105 @@
       <c r="F22" s="48"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="174" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="175"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="48"/>
+      <c r="H23" s="22"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="135"/>
-      <c r="E23" s="162">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="162">
         <f>D22</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="106"/>
-    </row>
-    <row r="25" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="177" t="s">
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="106"/>
+    </row>
+    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="174" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="178"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="174">
+      <c r="B26" s="175"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="172">
         <v>149073.01</v>
       </c>
-      <c r="E25" s="121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="177" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="178"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="168">
-        <v>0</v>
-      </c>
-      <c r="E26" s="121"/>
-    </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="29" t="s">
+      <c r="E26" s="121" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="174" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="175"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="168">
+        <v>0</v>
+      </c>
+      <c r="E27" s="121"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="135"/>
-      <c r="E27" s="99">
-        <f>SUM(D25:D26)</f>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="135"/>
+      <c r="E28" s="99">
+        <f>SUM(D26:D27)</f>
         <v>149073.01</v>
       </c>
-      <c r="G27" s="151"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="38" t="s">
+      <c r="G28" s="151"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="100"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="100"/>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="104"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="120">
-        <v>750368</v>
-      </c>
-      <c r="E30" s="121" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="120"/>
+      <c r="E30" s="104"/>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="120"/>
-      <c r="E31" s="104"/>
-    </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="120">
+        <v>0</v>
+      </c>
+      <c r="E31" s="121"/>
+    </row>
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>77</v>
       </c>
@@ -2004,566 +2015,549 @@
       <c r="D32" s="120"/>
       <c r="E32" s="104"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="120"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="29" t="s">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="104"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
         <v>2</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="99">
-        <f>SUM(D29:D33)</f>
-        <v>750368</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="38" t="s">
-        <v>34</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
       <c r="D35" s="42"/>
-      <c r="E35" s="102"/>
-    </row>
-    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="170" t="s">
+      <c r="E35" s="99">
+        <f>SUM(D30:D34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="102"/>
+    </row>
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="170" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="41">
-        <v>0</v>
-      </c>
-      <c r="E36" s="121"/>
-      <c r="J36" s="60"/>
-    </row>
-    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="29" t="s">
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="41">
+        <v>0</v>
+      </c>
+      <c r="E37" s="121"/>
+      <c r="J37" s="60"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="106">
-        <f>SUM(D36:D36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="38" t="s">
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="106">
+        <f>SUM(D37:D37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="102"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="B39" s="71"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="102"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="120">
-        <v>34240.639999999999</v>
-      </c>
-      <c r="E39" s="107"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="120">
+        <v>48318.25</v>
+      </c>
+      <c r="E40" s="107"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="120">
         <v>69000</v>
       </c>
-      <c r="E40" s="105"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="59" t="s">
+      <c r="E41" s="105"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="99">
-        <f>SUM(D39:D40)</f>
-        <v>103240.64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="109"/>
-    </row>
-    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="110"/>
-      <c r="E43" s="111">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="113"/>
-      <c r="F44" s="51"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="99">
+        <f>SUM(D40:D41)</f>
+        <v>117318.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="109"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="111">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="113"/>
+      <c r="F45" s="51"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="115">
-        <f>(SUM(E21:E43))</f>
-        <v>2402681.65</v>
-      </c>
-      <c r="F45" s="51"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-    </row>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="10"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="115">
+        <f>(SUM(E21:E44))</f>
+        <v>1166391.26</v>
+      </c>
+      <c r="F46" s="51"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D47" s="112"/>
       <c r="E47" s="112"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
+    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="112"/>
+      <c r="E48" s="112"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="116"/>
-      <c r="E48" s="117"/>
-    </row>
-    <row r="49" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="177"/>
-      <c r="B49" s="178"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="101"/>
-    </row>
-    <row r="50" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="177"/>
-      <c r="B50" s="178"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="116"/>
+      <c r="E49" s="117"/>
+    </row>
+    <row r="50" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="174"/>
+      <c r="B50" s="175"/>
       <c r="C50" s="5"/>
       <c r="D50" s="103"/>
       <c r="E50" s="101"/>
     </row>
-    <row r="51" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="182"/>
-      <c r="B51" s="183"/>
+    <row r="51" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="174"/>
+      <c r="B51" s="175"/>
       <c r="C51" s="5"/>
       <c r="D51" s="103"/>
       <c r="E51" s="101"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="122"/>
-      <c r="B52" s="123"/>
-      <c r="C52" s="60"/>
+    <row r="52" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="179"/>
+      <c r="B52" s="180"/>
+      <c r="C52" s="5"/>
       <c r="D52" s="103"/>
       <c r="E52" s="101"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="57"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63">
-        <f>SUM(D49:D52)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="32" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="122"/>
+      <c r="B53" s="123"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="101"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="57"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63">
+        <f>SUM(D50:D53)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="125"/>
-    </row>
-    <row r="57" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="125"/>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="72">
-        <f>E53+E56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="94" t="s">
+      <c r="B59" s="10"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="72">
+        <f>E54+E57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="B60" s="95">
-        <f>E45</f>
-        <v>2402681.65</v>
-      </c>
-      <c r="D60" s="51"/>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="94" t="s">
+      <c r="B61" s="95">
+        <f>E46</f>
+        <v>1166391.26</v>
+      </c>
+      <c r="D61" s="51"/>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="B61" s="95">
-        <f>E45-E43</f>
-        <v>1402681.65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="94" t="s">
+      <c r="B62" s="95">
+        <f>E46-E44</f>
+        <v>666391.26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="95">
-        <f>E58-E56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="94" t="s">
+      <c r="B63" s="95">
+        <f>E59-E57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="95">
-        <f>E58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="181" t="s">
+      <c r="B64" s="95">
+        <f>E59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="178" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="181"/>
-      <c r="C66" s="181"/>
-      <c r="D66" s="181"/>
-      <c r="E66" s="181"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="181"/>
-      <c r="B67" s="181"/>
-      <c r="C67" s="181"/>
-      <c r="D67" s="181"/>
-      <c r="E67" s="181"/>
-    </row>
-    <row r="68" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="181"/>
-      <c r="B68" s="181"/>
-      <c r="C68" s="181"/>
-      <c r="D68" s="181"/>
-      <c r="E68" s="181"/>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="185" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" s="186"/>
-      <c r="C70" s="186"/>
-      <c r="D70" s="186"/>
-      <c r="E70" s="187"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="188"/>
-      <c r="B71" s="189"/>
-      <c r="C71" s="189"/>
-      <c r="D71" s="189"/>
-      <c r="E71" s="190"/>
-    </row>
-    <row r="72" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="191"/>
-      <c r="B72" s="192"/>
-      <c r="C72" s="192"/>
-      <c r="D72" s="192"/>
-      <c r="E72" s="193"/>
-    </row>
-    <row r="73" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="163"/>
-      <c r="B73" s="163"/>
-      <c r="C73" s="163"/>
-      <c r="D73" s="163"/>
-      <c r="E73" s="163"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="165" t="s">
+      <c r="B67" s="178"/>
+      <c r="C67" s="178"/>
+      <c r="D67" s="178"/>
+      <c r="E67" s="178"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="178"/>
+      <c r="B68" s="178"/>
+      <c r="C68" s="178"/>
+      <c r="D68" s="178"/>
+      <c r="E68" s="178"/>
+    </row>
+    <row r="69" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="178"/>
+      <c r="B69" s="178"/>
+      <c r="C69" s="178"/>
+      <c r="D69" s="178"/>
+      <c r="E69" s="178"/>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="182" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" s="183"/>
+      <c r="C71" s="183"/>
+      <c r="D71" s="183"/>
+      <c r="E71" s="184"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="185"/>
+      <c r="B72" s="186"/>
+      <c r="C72" s="186"/>
+      <c r="D72" s="186"/>
+      <c r="E72" s="187"/>
+    </row>
+    <row r="73" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="188"/>
+      <c r="B73" s="189"/>
+      <c r="C73" s="189"/>
+      <c r="D73" s="189"/>
+      <c r="E73" s="190"/>
+    </row>
+    <row r="74" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="163"/>
+      <c r="B74" s="163"/>
+      <c r="C74" s="163"/>
+      <c r="D74" s="163"/>
+      <c r="E74" s="163"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="B74" s="166"/>
-      <c r="C74" s="23"/>
-    </row>
-    <row r="75" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="167" t="s">
+      <c r="B75" s="166"/>
+      <c r="C75" s="23"/>
+    </row>
+    <row r="76" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="167" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="124">
-        <v>1232001.3899999999</v>
-      </c>
-      <c r="C75" s="25"/>
-    </row>
-    <row r="76" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="24" t="s">
+      <c r="B76" s="124">
+        <v>484460.93000000017</v>
+      </c>
+      <c r="C76" s="25"/>
+    </row>
+    <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B76" s="47">
+      <c r="B77" s="47">
         <f>PRORRATEO!G35</f>
-        <v>1111121.19</v>
-      </c>
-      <c r="C76" s="23"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="24" t="s">
+        <v>1649630.34</v>
+      </c>
+      <c r="C77" s="23"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B77" s="47"/>
-      <c r="C77" s="23"/>
-    </row>
-    <row r="78" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B78" s="169">
-        <v>-99000</v>
-      </c>
+      <c r="B78" s="47"/>
       <c r="C78" s="23"/>
     </row>
-    <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" s="169">
-        <v>-270000</v>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="47">
+        <f>B98</f>
+        <v>0</v>
       </c>
       <c r="C79" s="23"/>
     </row>
-    <row r="80" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B80" s="169">
-        <v>-86980</v>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="47">
+        <v>0</v>
       </c>
       <c r="C80" s="23"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="47">
-        <f>B100</f>
-        <v>0</v>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="169">
+        <f>-B62</f>
+        <v>-666391.26</v>
       </c>
       <c r="C81" s="23"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="47">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" s="105">
+        <f>-(B63)</f>
         <v>0</v>
       </c>
       <c r="C82" s="23"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="46" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="124">
+        <f>SUM(B76:B82)</f>
+        <v>1467700.0100000005</v>
+      </c>
+      <c r="C83" s="26"/>
+      <c r="D83" s="151"/>
+      <c r="E83" s="151"/>
+      <c r="F83" s="151"/>
+    </row>
+    <row r="84" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="48"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="51"/>
+    </row>
+    <row r="85" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="49"/>
+      <c r="C85" s="26"/>
+    </row>
+    <row r="86" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="44"/>
+    </row>
+    <row r="87" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="40"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="54"/>
+    </row>
+    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" s="41">
+        <v>0</v>
+      </c>
+      <c r="C88" s="44"/>
+    </row>
+    <row r="89" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" s="40">
+        <v>0</v>
+      </c>
+      <c r="C89" s="26"/>
+      <c r="D89" s="51"/>
+    </row>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="169">
-        <f>-B61</f>
-        <v>-1402681.65</v>
-      </c>
-      <c r="C83" s="23"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="27" t="s">
+      <c r="B90" s="40">
+        <v>0</v>
+      </c>
+      <c r="C90" s="26"/>
+    </row>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B84" s="105">
-        <f>-(B62)</f>
-        <v>0</v>
-      </c>
-      <c r="C84" s="23"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B85" s="124">
-        <f>SUM(B75:B84)</f>
-        <v>484460.93000000017</v>
-      </c>
-      <c r="C85" s="26"/>
-      <c r="D85" s="151"/>
-      <c r="E85" s="151"/>
-      <c r="F85" s="151"/>
-    </row>
-    <row r="86" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="48"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="51"/>
-    </row>
-    <row r="87" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="49"/>
-      <c r="C87" s="26"/>
-    </row>
-    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="44"/>
-    </row>
-    <row r="89" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B89" s="40"/>
-      <c r="C89" s="44"/>
-      <c r="D89" s="54"/>
-    </row>
-    <row r="90" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B90" s="41">
-        <v>0</v>
-      </c>
-      <c r="C90" s="44"/>
-    </row>
-    <row r="91" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="B91" s="40">
         <v>0</v>
       </c>
-      <c r="C91" s="26"/>
-      <c r="D91" s="51"/>
-    </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B92" s="40">
-        <v>0</v>
-      </c>
-      <c r="C92" s="26"/>
-    </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B93" s="40">
-        <v>0</v>
-      </c>
-      <c r="C93" s="28"/>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="35" t="s">
+      <c r="C91" s="28"/>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B94" s="55">
-        <f>SUM(B90:B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C94" s="23"/>
-    </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A97" s="180" t="s">
+      <c r="B92" s="55">
+        <f>SUM(B88:B91)</f>
+        <v>0</v>
+      </c>
+      <c r="C92" s="23"/>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="B97" s="180"/>
-      <c r="C97" s="180"/>
-    </row>
-    <row r="98" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="180"/>
-      <c r="B98" s="180"/>
-      <c r="C98" s="180"/>
-    </row>
-    <row r="99" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="118"/>
-      <c r="B99" s="40"/>
-      <c r="C99" s="164">
+      <c r="B95" s="177"/>
+      <c r="C95" s="177"/>
+    </row>
+    <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="177"/>
+      <c r="B96" s="177"/>
+      <c r="C96" s="177"/>
+    </row>
+    <row r="97" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="118"/>
+      <c r="B97" s="40"/>
+      <c r="C97" s="164">
         <v>40000</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="52" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B100" s="119">
-        <f>SUM(B99:B99)</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="53"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M101" s="8"/>
-    </row>
-    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="179"/>
-      <c r="B102" s="179"/>
-      <c r="C102" s="179"/>
-      <c r="D102" s="179"/>
-      <c r="E102" s="179"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="179"/>
-      <c r="B103" s="179"/>
-      <c r="C103" s="179"/>
-      <c r="D103" s="179"/>
-      <c r="E103" s="179"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="179"/>
-      <c r="B104" s="179"/>
-      <c r="C104" s="179"/>
-      <c r="D104" s="179"/>
-      <c r="E104" s="179"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="179"/>
-      <c r="B105" s="179"/>
-      <c r="C105" s="179"/>
-      <c r="D105" s="179"/>
-      <c r="E105" s="179"/>
+      <c r="B98" s="119">
+        <f>SUM(B97:B97)</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="53"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M99" s="8"/>
+    </row>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="176"/>
+      <c r="B100" s="176"/>
+      <c r="C100" s="176"/>
+      <c r="D100" s="176"/>
+      <c r="E100" s="176"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="176"/>
+      <c r="B101" s="176"/>
+      <c r="C101" s="176"/>
+      <c r="D101" s="176"/>
+      <c r="E101" s="176"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="176"/>
+      <c r="B102" s="176"/>
+      <c r="C102" s="176"/>
+      <c r="D102" s="176"/>
+      <c r="E102" s="176"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="176"/>
+      <c r="B103" s="176"/>
+      <c r="C103" s="176"/>
+      <c r="D103" s="176"/>
+      <c r="E103" s="176"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A102:E105"/>
-    <mergeCell ref="A97:C98"/>
-    <mergeCell ref="A66:E68"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A100:E103"/>
+    <mergeCell ref="A95:C96"/>
+    <mergeCell ref="A67:E69"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A70:E72"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A71:E73"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2574,36 +2568,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="194" t="s">
+      <c r="C1" s="204" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2615,13 +2609,13 @@
       <c r="O1" s="62"/>
       <c r="P1" s="22"/>
     </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="205"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2633,13 +2627,13 @@
       <c r="O2" s="62"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2647,25 +2641,25 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="196">
+      <c r="L3" s="206">
         <f>Q3</f>
-        <v>2402681.65</v>
-      </c>
-      <c r="M3" s="196"/>
+        <v>1166391.26</v>
+      </c>
+      <c r="M3" s="206"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
       <c r="Q3">
-        <v>2402681.65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1166391.26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2673,99 +2667,99 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="197"/>
-      <c r="M4" s="197"/>
+      <c r="L4" s="207"/>
+      <c r="M4" s="207"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
-    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="202" t="s">
+    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="210" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="203"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="O5" s="204"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="198" t="s">
+      <c r="B5" s="211"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="M5" s="211"/>
+      <c r="N5" s="211"/>
+      <c r="O5" s="212"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="200" t="s">
+      <c r="B6" s="192" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="200" t="s">
+      <c r="C6" s="192" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="200" t="s">
+      <c r="D6" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="200" t="s">
+      <c r="E6" s="192" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="192" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="200" t="s">
+      <c r="G6" s="192" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="216" t="s">
+      <c r="H6" s="201" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="216" t="s">
+      <c r="I6" s="201" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="211" t="s">
+      <c r="J6" s="196" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="211" t="s">
+      <c r="K6" s="196" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="214" t="s">
+      <c r="L6" s="199" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="209" t="s">
+      <c r="N6" s="194" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="205" t="s">
+      <c r="O6" s="213" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="199"/>
-      <c r="B7" s="201"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="201"/>
-      <c r="G7" s="201"/>
-      <c r="H7" s="217"/>
-      <c r="I7" s="217"/>
-      <c r="J7" s="212"/>
-      <c r="K7" s="213"/>
-      <c r="L7" s="215"/>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="209"/>
+      <c r="B7" s="203"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="203"/>
+      <c r="G7" s="203"/>
+      <c r="H7" s="202"/>
+      <c r="I7" s="202"/>
+      <c r="J7" s="197"/>
+      <c r="K7" s="198"/>
+      <c r="L7" s="200"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="N7" s="210"/>
-      <c r="O7" s="206"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="195"/>
+      <c r="O7" s="214"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2780,18 +2774,18 @@
         <v>6.8</v>
       </c>
       <c r="F8" s="78">
-        <v>507403.01</v>
+        <v>769303.01</v>
       </c>
       <c r="G8" s="79">
-        <v>0</v>
+        <v>769303.01</v>
       </c>
       <c r="H8" s="80">
         <f>F8-G8</f>
-        <v>507403.01</v>
+        <v>0</v>
       </c>
       <c r="I8" s="80">
         <f>IF(H8&gt;0,H8*15%,0)</f>
-        <v>76110.451499999996</v>
+        <v>0</v>
       </c>
       <c r="J8" s="127">
         <f t="shared" ref="J8:J33" si="0">L$4*E8/100</f>
@@ -2799,28 +2793,28 @@
       </c>
       <c r="K8" s="127">
         <f t="shared" ref="K8:K33" si="1">L$3*E8/100</f>
-        <v>163382.35219999999</v>
+        <v>79314.605679999993</v>
       </c>
       <c r="L8" s="82">
         <v>0</v>
       </c>
       <c r="M8" s="83">
         <f t="shared" ref="M8:M33" si="2">ROUND(SUM(H8:L8),0) + P8</f>
-        <v>746896.01</v>
+        <v>79315.009999999995</v>
       </c>
       <c r="N8" s="84">
         <f>ROUND(M8*6% + M8,0) + P8</f>
-        <v>791710.01</v>
+        <v>84074.01</v>
       </c>
       <c r="O8" s="85">
         <f>ROUND(M8*3%,0) + M8</f>
-        <v>769303.01</v>
+        <v>81694.009999999995</v>
       </c>
       <c r="P8" s="51">
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
         <v>9</v>
       </c>
@@ -2836,14 +2830,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F9" s="79">
-        <v>-282333.98</v>
+        <v>-159796.98000000001</v>
       </c>
       <c r="G9" s="79">
         <v>0</v>
       </c>
       <c r="H9" s="96">
         <f>F9-G9</f>
-        <v>-282333.98</v>
+        <v>-159796.98000000001</v>
       </c>
       <c r="I9" s="96">
         <f>IF(H9&gt;0,H9*15%,0)</f>
@@ -2855,22 +2849,22 @@
       </c>
       <c r="K9" s="146">
         <f t="shared" si="1"/>
-        <v>122536.76414999999</v>
+        <v>59485.954259999999</v>
       </c>
       <c r="L9" s="147">
         <v>0</v>
       </c>
       <c r="M9" s="148">
         <f t="shared" si="2"/>
-        <v>-159796.98000000001</v>
+        <v>-100310.98</v>
       </c>
       <c r="N9" s="149">
         <f t="shared" ref="N9:N33" si="3">ROUND(M9*6% + M9,0) + P9</f>
-        <v>-169384.98</v>
+        <v>-106329.98</v>
       </c>
       <c r="O9" s="150">
         <f t="shared" ref="O9:O33" si="4">ROUND(M9*3%,0) + M9</f>
-        <v>-164590.98000000001</v>
+        <v>-103319.98</v>
       </c>
       <c r="P9" s="51">
         <f>P8+0.01</f>
@@ -2881,7 +2875,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
         <v>9</v>
       </c>
@@ -2897,11 +2891,10 @@
         <v>5.6</v>
       </c>
       <c r="F10" s="79">
-        <v>93457.03</v>
-      </c>
-      <c r="G10" s="173">
-        <f>F10</f>
-        <v>93457.03</v>
+        <v>138587.03</v>
+      </c>
+      <c r="G10" s="79">
+        <v>138587.03</v>
       </c>
       <c r="H10" s="96">
         <f>F10-G10</f>
@@ -2917,29 +2910,29 @@
       </c>
       <c r="K10" s="146">
         <f t="shared" si="1"/>
-        <v>134550.17239999998</v>
+        <v>65317.910559999997</v>
       </c>
       <c r="L10" s="147">
         <v>0</v>
       </c>
       <c r="M10" s="148">
         <f t="shared" si="2"/>
-        <v>134550.03</v>
+        <v>65318.03</v>
       </c>
       <c r="N10" s="149">
         <f t="shared" si="3"/>
-        <v>142623.03</v>
+        <v>69237.03</v>
       </c>
       <c r="O10" s="150">
         <f t="shared" si="4"/>
-        <v>138587.03</v>
+        <v>67278.03</v>
       </c>
       <c r="P10" s="51">
         <f t="shared" ref="P10:P33" si="6">P9+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -2955,14 +2948,14 @@
         <v>2.8</v>
       </c>
       <c r="F11" s="78">
-        <v>-1118791.96</v>
+        <v>-1051516.96</v>
       </c>
       <c r="G11" s="79">
         <v>0</v>
       </c>
       <c r="H11" s="80">
         <f t="shared" ref="H11:H16" si="7">F11-G11</f>
-        <v>-1118791.96</v>
+        <v>-1051516.96</v>
       </c>
       <c r="I11" s="80">
         <f t="shared" ref="I11:I33" si="8">IF(H11&gt;0,H11*15%,0)</f>
@@ -2974,22 +2967,22 @@
       </c>
       <c r="K11" s="127">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L11" s="82">
         <v>0</v>
       </c>
       <c r="M11" s="83">
         <f t="shared" si="2"/>
-        <v>-1051516.96</v>
+        <v>-1018857.96</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="3"/>
-        <v>-1114607.96</v>
+        <v>-1079988.96</v>
       </c>
       <c r="O11" s="85">
         <f t="shared" si="4"/>
-        <v>-1083062.96</v>
+        <v>-1049423.96</v>
       </c>
       <c r="P11" s="51">
         <f t="shared" si="6"/>
@@ -2999,7 +2992,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -3015,19 +3008,16 @@
         <v>2.8</v>
       </c>
       <c r="F12" s="78">
-        <v>133955.04999999999</v>
-      </c>
-      <c r="G12" s="173">
-        <f>137974.05</f>
-        <v>137974.04999999999</v>
-      </c>
+        <v>63256.05</v>
+      </c>
+      <c r="G12" s="79"/>
       <c r="H12" s="80">
         <f t="shared" si="7"/>
-        <v>-4019</v>
+        <v>63256.05</v>
       </c>
       <c r="I12" s="80">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9488.4074999999993</v>
       </c>
       <c r="J12" s="127">
         <f t="shared" si="0"/>
@@ -3035,22 +3025,22 @@
       </c>
       <c r="K12" s="127">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L12" s="82">
         <v>0</v>
       </c>
       <c r="M12" s="83">
         <f t="shared" si="2"/>
-        <v>63256.05</v>
+        <v>105403.05</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="3"/>
-        <v>67051.05</v>
+        <v>111727.05</v>
       </c>
       <c r="O12" s="85">
         <f t="shared" si="4"/>
-        <v>65154.05</v>
+        <v>108565.05</v>
       </c>
       <c r="P12" s="51">
         <f t="shared" si="6"/>
@@ -3058,7 +3048,7 @@
       </c>
       <c r="R12" s="51"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3074,14 +3064,15 @@
         <v>2.8</v>
       </c>
       <c r="F13" s="78">
-        <v>-27483.94</v>
+        <v>39791.06</v>
       </c>
       <c r="G13" s="79">
-        <v>0</v>
+        <f>46728.06+74000.06</f>
+        <v>120728.12</v>
       </c>
       <c r="H13" s="80">
         <f t="shared" si="7"/>
-        <v>-27483.94</v>
+        <v>-80937.06</v>
       </c>
       <c r="I13" s="80">
         <f t="shared" si="8"/>
@@ -3093,22 +3084,22 @@
       </c>
       <c r="K13" s="127">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L13" s="82">
         <v>0</v>
       </c>
       <c r="M13" s="83">
         <f t="shared" si="2"/>
-        <v>39791.06</v>
+        <v>-48277.94</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="3"/>
-        <v>42179.06</v>
+        <v>-51174.94</v>
       </c>
       <c r="O13" s="85">
         <f t="shared" si="4"/>
-        <v>40985.06</v>
+        <v>-49725.94</v>
       </c>
       <c r="P13" s="51">
         <f t="shared" si="6"/>
@@ -3118,7 +3109,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -3134,18 +3125,18 @@
         <v>4</v>
       </c>
       <c r="F14" s="154">
-        <v>2985045.07</v>
+        <v>3528909.07</v>
       </c>
       <c r="G14" s="154">
         <v>0</v>
       </c>
       <c r="H14" s="155">
         <f t="shared" si="7"/>
-        <v>2985045.07</v>
+        <v>3528909.07</v>
       </c>
       <c r="I14" s="155">
         <f t="shared" si="8"/>
-        <v>447756.76049999997</v>
+        <v>529336.36049999995</v>
       </c>
       <c r="J14" s="156">
         <f t="shared" si="0"/>
@@ -3153,29 +3144,29 @@
       </c>
       <c r="K14" s="156">
         <f t="shared" si="1"/>
-        <v>96107.266000000003</v>
+        <v>46655.650399999999</v>
       </c>
       <c r="L14" s="157">
         <v>0</v>
       </c>
       <c r="M14" s="158">
         <f t="shared" si="2"/>
-        <v>3528909.07</v>
+        <v>4104901.07</v>
       </c>
       <c r="N14" s="159">
         <f t="shared" si="3"/>
-        <v>3740644.07</v>
+        <v>4351195.07</v>
       </c>
       <c r="O14" s="160">
         <f t="shared" si="4"/>
-        <v>3634776.07</v>
+        <v>4228048.07</v>
       </c>
       <c r="P14" s="51">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3191,18 +3182,18 @@
         <v>3.2</v>
       </c>
       <c r="F15" s="138">
-        <v>53404.08</v>
+        <v>138301.07999999999</v>
       </c>
       <c r="G15" s="138">
         <v>0</v>
       </c>
       <c r="H15" s="139">
         <f t="shared" si="7"/>
-        <v>53404.08</v>
+        <v>138301.07999999999</v>
       </c>
       <c r="I15" s="139">
         <f t="shared" si="8"/>
-        <v>8010.6120000000001</v>
+        <v>20745.161999999997</v>
       </c>
       <c r="J15" s="140">
         <f t="shared" si="0"/>
@@ -3210,29 +3201,29 @@
       </c>
       <c r="K15" s="140">
         <f t="shared" si="1"/>
-        <v>76885.8128</v>
+        <v>37324.520320000003</v>
       </c>
       <c r="L15" s="141">
         <v>0</v>
       </c>
       <c r="M15" s="142">
         <f t="shared" si="2"/>
-        <v>138301.07999999999</v>
+        <v>196371.08</v>
       </c>
       <c r="N15" s="143">
         <f t="shared" si="3"/>
-        <v>146599.07999999999</v>
+        <v>208153.08</v>
       </c>
       <c r="O15" s="144">
         <f t="shared" si="4"/>
-        <v>142450.07999999999</v>
+        <v>202262.08</v>
       </c>
       <c r="P15" s="51">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
@@ -3248,18 +3239,18 @@
         <v>2.8</v>
       </c>
       <c r="F16" s="154">
-        <v>2600810.09</v>
+        <v>3058207.09</v>
       </c>
       <c r="G16" s="154">
         <v>0</v>
       </c>
       <c r="H16" s="155">
         <f t="shared" si="7"/>
-        <v>2600810.09</v>
+        <v>3058207.09</v>
       </c>
       <c r="I16" s="155">
         <f t="shared" si="8"/>
-        <v>390121.51349999994</v>
+        <v>458731.06349999999</v>
       </c>
       <c r="J16" s="156">
         <f t="shared" si="0"/>
@@ -3267,29 +3258,29 @@
       </c>
       <c r="K16" s="156">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L16" s="157">
         <v>0</v>
       </c>
       <c r="M16" s="158">
         <f t="shared" si="2"/>
-        <v>3058207.09</v>
+        <v>3549597.09</v>
       </c>
       <c r="N16" s="159">
         <f t="shared" si="3"/>
-        <v>3241700.09</v>
+        <v>3762573.09</v>
       </c>
       <c r="O16" s="160">
         <f t="shared" si="4"/>
-        <v>3149953.09</v>
+        <v>3656085.09</v>
       </c>
       <c r="P16" s="51">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -3305,7 +3296,7 @@
         <v>2.8</v>
       </c>
       <c r="F17" s="79">
-        <v>46728.1</v>
+        <v>67275.100000000006</v>
       </c>
       <c r="G17" s="79" t="s">
         <v>76</v>
@@ -3321,18 +3312,18 @@
       </c>
       <c r="K17" s="127">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L17" s="82">
         <v>0</v>
       </c>
       <c r="M17" s="83">
         <f t="shared" si="2"/>
-        <v>67275.100000000006</v>
+        <v>32659.1</v>
       </c>
       <c r="N17" s="84">
         <f t="shared" si="3"/>
-        <v>71312.100000000006</v>
+        <v>34619.1</v>
       </c>
       <c r="O17" s="79" t="s">
         <v>76</v>
@@ -3342,7 +3333,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -3358,7 +3349,7 @@
         <v>2.8</v>
       </c>
       <c r="F18" s="79">
-        <v>46728.11</v>
+        <v>67275.11</v>
       </c>
       <c r="G18" s="79" t="s">
         <v>76</v>
@@ -3374,18 +3365,18 @@
       </c>
       <c r="K18" s="127">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L18" s="82">
         <v>0</v>
       </c>
       <c r="M18" s="83">
         <f t="shared" si="2"/>
-        <v>67275.11</v>
+        <v>32659.11</v>
       </c>
       <c r="N18" s="84">
         <f t="shared" si="3"/>
-        <v>71312.11</v>
+        <v>34619.11</v>
       </c>
       <c r="O18" s="79" t="s">
         <v>76</v>
@@ -3395,7 +3386,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60" t="s">
         <v>14</v>
       </c>
@@ -3411,19 +3402,16 @@
         <v>2.8</v>
       </c>
       <c r="F19" s="79">
-        <v>135771.12</v>
-      </c>
-      <c r="G19" s="173">
-        <f>F19</f>
-        <v>135771.12</v>
-      </c>
+        <v>67275.12</v>
+      </c>
+      <c r="G19" s="79"/>
       <c r="H19" s="96">
         <f t="shared" ref="H19:H31" si="9">F19-G19</f>
-        <v>0</v>
+        <v>67275.12</v>
       </c>
       <c r="I19" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10091.267999999998</v>
       </c>
       <c r="J19" s="146">
         <f t="shared" si="0"/>
@@ -3431,37 +3419,37 @@
       </c>
       <c r="K19" s="146">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L19" s="147">
         <v>0</v>
       </c>
       <c r="M19" s="148">
         <f t="shared" si="2"/>
-        <v>67275.12</v>
+        <v>110025.12</v>
       </c>
       <c r="N19" s="149">
         <f t="shared" si="3"/>
-        <v>71312.12</v>
+        <v>116627.12</v>
       </c>
       <c r="O19" s="150">
         <f t="shared" si="4"/>
-        <v>69293.119999999995</v>
+        <v>113326.12</v>
       </c>
       <c r="P19" s="51">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="175">
+      <c r="B20" s="68">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="C20" s="175" t="s">
+      <c r="C20" s="68" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="86"/>
@@ -3469,18 +3457,18 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F20" s="79">
-        <v>1666904.13</v>
-      </c>
-      <c r="G20" s="173">
-        <v>141029.64000000001</v>
+        <v>1877292.13</v>
+      </c>
+      <c r="G20" s="79">
+        <v>500000</v>
       </c>
       <c r="H20" s="96">
         <f t="shared" si="9"/>
-        <v>1525874.4899999998</v>
+        <v>1377292.13</v>
       </c>
       <c r="I20" s="96">
         <f t="shared" si="8"/>
-        <v>228881.17349999995</v>
+        <v>206593.81949999998</v>
       </c>
       <c r="J20" s="146">
         <f t="shared" si="0"/>
@@ -3488,22 +3476,22 @@
       </c>
       <c r="K20" s="146">
         <f t="shared" si="1"/>
-        <v>122536.76414999999</v>
+        <v>59485.954259999999</v>
       </c>
       <c r="L20" s="147">
         <v>0</v>
       </c>
       <c r="M20" s="148">
         <f t="shared" si="2"/>
-        <v>1877292.13</v>
+        <v>1643372.13</v>
       </c>
       <c r="N20" s="149">
         <f t="shared" si="3"/>
-        <v>1989930.13</v>
+        <v>1741974.13</v>
       </c>
       <c r="O20" s="150">
         <f t="shared" si="4"/>
-        <v>1933611.13</v>
+        <v>1692673.13</v>
       </c>
       <c r="P20" s="51">
         <f t="shared" si="6"/>
@@ -3513,7 +3501,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
@@ -3529,18 +3517,18 @@
         <v>2.6</v>
       </c>
       <c r="F21" s="154">
-        <v>1762210.14</v>
+        <v>2089011.14</v>
       </c>
       <c r="G21" s="154">
         <v>0</v>
       </c>
       <c r="H21" s="155">
         <f t="shared" si="9"/>
-        <v>1762210.14</v>
+        <v>2089011.14</v>
       </c>
       <c r="I21" s="155">
         <f t="shared" si="8"/>
-        <v>264331.52099999995</v>
+        <v>313351.67099999997</v>
       </c>
       <c r="J21" s="156">
         <f t="shared" si="0"/>
@@ -3548,22 +3536,22 @@
       </c>
       <c r="K21" s="156">
         <f t="shared" si="1"/>
-        <v>62469.722900000001</v>
+        <v>30326.172760000001</v>
       </c>
       <c r="L21" s="157">
         <v>0</v>
       </c>
       <c r="M21" s="158">
         <f t="shared" si="2"/>
-        <v>2089011.14</v>
+        <v>2432689.14</v>
       </c>
       <c r="N21" s="159">
         <f t="shared" si="3"/>
-        <v>2214352.14</v>
+        <v>2578650.14</v>
       </c>
       <c r="O21" s="160">
         <f t="shared" si="4"/>
-        <v>2151681.1399999997</v>
+        <v>2505670.14</v>
       </c>
       <c r="P21" s="51">
         <f t="shared" si="6"/>
@@ -3573,7 +3561,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
@@ -3589,19 +3577,16 @@
         <v>2.8</v>
       </c>
       <c r="F22" s="79">
-        <v>492118.15</v>
-      </c>
-      <c r="G22" s="173">
-        <f>135138.15+270000+86980</f>
-        <v>492118.15</v>
-      </c>
+        <v>67275.149999999994</v>
+      </c>
+      <c r="G22" s="79"/>
       <c r="H22" s="96">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>67275.149999999994</v>
       </c>
       <c r="I22" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10091.272499999999</v>
       </c>
       <c r="J22" s="146">
         <f t="shared" si="0"/>
@@ -3609,29 +3594,29 @@
       </c>
       <c r="K22" s="146">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L22" s="147">
         <v>0</v>
       </c>
       <c r="M22" s="148">
         <f t="shared" si="2"/>
-        <v>67275.149999999994</v>
+        <v>110025.15</v>
       </c>
       <c r="N22" s="149">
         <f t="shared" si="3"/>
-        <v>71312.149999999994</v>
+        <v>116627.15</v>
       </c>
       <c r="O22" s="150">
         <f t="shared" si="4"/>
-        <v>69293.149999999994</v>
+        <v>113326.15</v>
       </c>
       <c r="P22" s="51">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
@@ -3647,14 +3632,12 @@
         <v>2.6</v>
       </c>
       <c r="F23" s="78">
-        <v>-436483.84000000003</v>
-      </c>
-      <c r="G23" s="173">
-        <v>44000</v>
-      </c>
+        <v>-418013.84</v>
+      </c>
+      <c r="G23" s="79"/>
       <c r="H23" s="80">
         <f t="shared" si="9"/>
-        <v>-480483.84000000003</v>
+        <v>-418013.84</v>
       </c>
       <c r="I23" s="80">
         <f t="shared" si="8"/>
@@ -3666,22 +3649,22 @@
       </c>
       <c r="K23" s="127">
         <f t="shared" si="1"/>
-        <v>62469.722900000001</v>
+        <v>30326.172760000001</v>
       </c>
       <c r="L23" s="82">
         <v>0</v>
       </c>
       <c r="M23" s="83">
         <f t="shared" si="2"/>
-        <v>-418013.84</v>
+        <v>-387687.84</v>
       </c>
       <c r="N23" s="84">
         <f t="shared" si="3"/>
-        <v>-443094.84</v>
+        <v>-410948.84</v>
       </c>
       <c r="O23" s="85">
         <f t="shared" si="4"/>
-        <v>-430553.84</v>
+        <v>-399318.84</v>
       </c>
       <c r="P23" s="51">
         <f t="shared" si="6"/>
@@ -3689,7 +3672,7 @@
       </c>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
         <v>16</v>
       </c>
@@ -3705,16 +3688,16 @@
         <v>4.5</v>
       </c>
       <c r="F24" s="154">
-        <v>2650779.17</v>
+        <v>3156517.17</v>
       </c>
       <c r="G24" s="154"/>
       <c r="H24" s="155">
         <f t="shared" si="9"/>
-        <v>2650779.17</v>
+        <v>3156517.17</v>
       </c>
       <c r="I24" s="155">
         <f t="shared" si="8"/>
-        <v>397616.87549999997</v>
+        <v>473477.57549999998</v>
       </c>
       <c r="J24" s="156">
         <f t="shared" si="0"/>
@@ -3722,29 +3705,29 @@
       </c>
       <c r="K24" s="156">
         <f t="shared" si="1"/>
-        <v>108120.67424999998</v>
+        <v>52487.606699999997</v>
       </c>
       <c r="L24" s="157">
         <v>0</v>
       </c>
       <c r="M24" s="158">
         <f t="shared" si="2"/>
-        <v>3156517.17</v>
+        <v>3682482.17</v>
       </c>
       <c r="N24" s="159">
         <f t="shared" si="3"/>
-        <v>3345908.17</v>
+        <v>3903431.17</v>
       </c>
       <c r="O24" s="160">
         <f t="shared" si="4"/>
-        <v>3251213.17</v>
+        <v>3792956.17</v>
       </c>
       <c r="P24" s="51">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>17</v>
       </c>
@@ -3760,18 +3743,19 @@
         <v>2.8</v>
       </c>
       <c r="F25" s="79">
-        <v>46728.18</v>
+        <v>121012.18</v>
       </c>
       <c r="G25" s="79">
-        <v>0</v>
+        <f>F25</f>
+        <v>121012.18</v>
       </c>
       <c r="H25" s="96">
         <f t="shared" si="9"/>
-        <v>46728.18</v>
+        <v>0</v>
       </c>
       <c r="I25" s="96">
         <f t="shared" si="8"/>
-        <v>7009.2269999999999</v>
+        <v>0</v>
       </c>
       <c r="J25" s="146">
         <f t="shared" si="0"/>
@@ -3779,29 +3763,29 @@
       </c>
       <c r="K25" s="146">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L25" s="147">
         <v>0</v>
       </c>
       <c r="M25" s="148">
         <f t="shared" si="2"/>
-        <v>121012.18</v>
+        <v>32659.18</v>
       </c>
       <c r="N25" s="149">
         <f t="shared" si="3"/>
-        <v>128273.18</v>
+        <v>34619.18</v>
       </c>
       <c r="O25" s="150">
         <f t="shared" si="4"/>
-        <v>124642.18</v>
+        <v>33639.18</v>
       </c>
       <c r="P25" s="51">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60" t="s">
         <v>17</v>
       </c>
@@ -3817,16 +3801,16 @@
         <v>2.8</v>
       </c>
       <c r="F26" s="79">
-        <v>808011.19</v>
+        <v>996488.19</v>
       </c>
       <c r="G26" s="79"/>
       <c r="H26" s="96">
         <f t="shared" si="9"/>
-        <v>808011.19</v>
+        <v>996488.19</v>
       </c>
       <c r="I26" s="96">
         <f t="shared" si="8"/>
-        <v>121201.67849999998</v>
+        <v>149473.2285</v>
       </c>
       <c r="J26" s="146">
         <f t="shared" si="0"/>
@@ -3834,29 +3818,29 @@
       </c>
       <c r="K26" s="146">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L26" s="147">
         <v>0</v>
       </c>
       <c r="M26" s="148">
         <f t="shared" si="2"/>
-        <v>996488.19</v>
+        <v>1178620.19</v>
       </c>
       <c r="N26" s="149">
         <f t="shared" si="3"/>
-        <v>1056277.19</v>
+        <v>1249337.19</v>
       </c>
       <c r="O26" s="150">
         <f t="shared" si="4"/>
-        <v>1026383.19</v>
+        <v>1213979.19</v>
       </c>
       <c r="P26" s="51">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>18</v>
       </c>
@@ -3872,19 +3856,16 @@
         <v>2.8</v>
       </c>
       <c r="F27" s="79">
-        <v>66771.199999999997</v>
-      </c>
-      <c r="G27" s="173">
-        <f>F27</f>
-        <v>66771.199999999997</v>
-      </c>
+        <v>67275.199999999997</v>
+      </c>
+      <c r="G27" s="79"/>
       <c r="H27" s="96">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>67275.199999999997</v>
       </c>
       <c r="I27" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10091.279999999999</v>
       </c>
       <c r="J27" s="146">
         <f t="shared" si="0"/>
@@ -3892,29 +3873,29 @@
       </c>
       <c r="K27" s="146">
         <f t="shared" si="1"/>
-        <v>67275.086199999991</v>
+        <v>32658.955279999998</v>
       </c>
       <c r="L27" s="147">
         <v>0</v>
       </c>
       <c r="M27" s="148">
         <f t="shared" si="2"/>
-        <v>67275.199999999997</v>
+        <v>110025.2</v>
       </c>
       <c r="N27" s="149">
         <f t="shared" si="3"/>
-        <v>71312.2</v>
+        <v>116627.2</v>
       </c>
       <c r="O27" s="150">
         <f t="shared" si="4"/>
-        <v>69293.2</v>
+        <v>113326.2</v>
       </c>
       <c r="P27" s="51">
         <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60" t="s">
         <v>19</v>
       </c>
@@ -3930,18 +3911,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="154">
-        <v>2238784.21</v>
+        <v>2646682.21</v>
       </c>
       <c r="G28" s="154">
         <v>0</v>
       </c>
       <c r="H28" s="155">
         <f t="shared" si="9"/>
-        <v>2238784.21</v>
+        <v>2646682.21</v>
       </c>
       <c r="I28" s="155">
         <f t="shared" si="8"/>
-        <v>335817.63149999996</v>
+        <v>397002.33149999997</v>
       </c>
       <c r="J28" s="156">
         <f t="shared" si="0"/>
@@ -3949,29 +3930,29 @@
       </c>
       <c r="K28" s="156">
         <f t="shared" si="1"/>
-        <v>72080.449499999988</v>
+        <v>34991.737800000003</v>
       </c>
       <c r="L28" s="157">
         <v>0</v>
       </c>
       <c r="M28" s="158">
         <f t="shared" si="2"/>
-        <v>2646682.21</v>
+        <v>3078676.21</v>
       </c>
       <c r="N28" s="159">
         <f t="shared" si="3"/>
-        <v>2805483.21</v>
+        <v>3263397.21</v>
       </c>
       <c r="O28" s="160">
         <f t="shared" si="4"/>
-        <v>2726082.21</v>
+        <v>3171036.21</v>
       </c>
       <c r="P28" s="51">
         <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60" t="s">
         <v>20</v>
       </c>
@@ -3987,18 +3968,18 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="F29" s="154">
-        <v>3059672.22</v>
+        <v>3617133.22</v>
       </c>
       <c r="G29" s="154">
         <v>0</v>
       </c>
       <c r="H29" s="155">
         <f t="shared" si="9"/>
-        <v>3059672.22</v>
+        <v>3617133.22</v>
       </c>
       <c r="I29" s="155">
         <f t="shared" si="8"/>
-        <v>458950.83300000004</v>
+        <v>542569.98300000001</v>
       </c>
       <c r="J29" s="156">
         <f t="shared" si="0"/>
@@ -4006,29 +3987,29 @@
       </c>
       <c r="K29" s="156">
         <f t="shared" si="1"/>
-        <v>98509.947649999987</v>
+        <v>47822.041659999995</v>
       </c>
       <c r="L29" s="157">
         <v>0</v>
       </c>
       <c r="M29" s="158">
         <f t="shared" si="2"/>
-        <v>3617133.22</v>
+        <v>4207525.22</v>
       </c>
       <c r="N29" s="159">
         <f t="shared" si="3"/>
-        <v>3834161.22</v>
+        <v>4459977.22</v>
       </c>
       <c r="O29" s="160">
         <f t="shared" si="4"/>
-        <v>3725647.22</v>
+        <v>4333751.22</v>
       </c>
       <c r="P29" s="51">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>21</v>
       </c>
@@ -4044,16 +4025,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F30" s="78">
-        <v>1558208.23</v>
+        <v>1914476.23</v>
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="80">
         <f t="shared" si="9"/>
-        <v>1558208.23</v>
+        <v>1914476.23</v>
       </c>
       <c r="I30" s="80">
         <f t="shared" si="8"/>
-        <v>233731.23449999999</v>
+        <v>287171.43449999997</v>
       </c>
       <c r="J30" s="127">
         <f t="shared" si="0"/>
@@ -4061,29 +4042,29 @@
       </c>
       <c r="K30" s="127">
         <f t="shared" si="1"/>
-        <v>122536.76414999999</v>
+        <v>59485.954259999999</v>
       </c>
       <c r="L30" s="82">
         <v>0</v>
       </c>
       <c r="M30" s="83">
         <f t="shared" si="2"/>
-        <v>1914476.23</v>
+        <v>2261134.23</v>
       </c>
       <c r="N30" s="84">
         <f t="shared" si="3"/>
-        <v>2029345.23</v>
+        <v>2396802.23</v>
       </c>
       <c r="O30" s="85">
         <f t="shared" si="4"/>
-        <v>1971910.23</v>
+        <v>2328968.23</v>
       </c>
       <c r="P30" s="51">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
@@ -4099,18 +4080,18 @@
         <v>5.9</v>
       </c>
       <c r="F31" s="154">
-        <v>4402941.24</v>
+        <v>5205141.24</v>
       </c>
       <c r="G31" s="154">
         <v>0</v>
       </c>
       <c r="H31" s="155">
         <f t="shared" si="9"/>
-        <v>4402941.24</v>
+        <v>5205141.24</v>
       </c>
       <c r="I31" s="155">
         <f t="shared" si="8"/>
-        <v>660441.18599999999</v>
+        <v>780771.18599999999</v>
       </c>
       <c r="J31" s="156">
         <f t="shared" si="0"/>
@@ -4118,29 +4099,29 @@
       </c>
       <c r="K31" s="156">
         <f t="shared" si="1"/>
-        <v>141758.21734999999</v>
+        <v>68817.084340000001</v>
       </c>
       <c r="L31" s="157">
         <v>0</v>
       </c>
       <c r="M31" s="158">
         <f t="shared" si="2"/>
-        <v>5205141.24</v>
+        <v>6054730.2400000002</v>
       </c>
       <c r="N31" s="159">
         <f t="shared" si="3"/>
-        <v>5517450.2400000002</v>
+        <v>6418014.2400000002</v>
       </c>
       <c r="O31" s="160">
         <f t="shared" si="4"/>
-        <v>5361295.24</v>
+        <v>6236372.2400000002</v>
       </c>
       <c r="P31" s="51">
         <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>24</v>
       </c>
@@ -4156,7 +4137,7 @@
         <v>5.5</v>
       </c>
       <c r="F32" s="79">
-        <v>91788.25</v>
+        <v>132147.25</v>
       </c>
       <c r="G32" s="79" t="s">
         <v>76</v>
@@ -4172,18 +4153,18 @@
       </c>
       <c r="K32" s="127">
         <f t="shared" si="1"/>
-        <v>132147.49075</v>
+        <v>64151.5193</v>
       </c>
       <c r="L32" s="82">
         <v>0</v>
       </c>
       <c r="M32" s="131">
         <f t="shared" si="2"/>
-        <v>132147.25</v>
+        <v>64152.25</v>
       </c>
       <c r="N32" s="132">
         <f t="shared" si="3"/>
-        <v>140076.25</v>
+        <v>68001.25</v>
       </c>
       <c r="O32" s="79" t="s">
         <v>76</v>
@@ -4193,7 +4174,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -4209,18 +4190,18 @@
         <v>6.1</v>
       </c>
       <c r="F33" s="154">
-        <v>4898539.26</v>
+        <v>5779884.2599999998</v>
       </c>
       <c r="G33" s="154">
         <v>0</v>
       </c>
       <c r="H33" s="155">
         <f>F33-G33</f>
-        <v>4898539.26</v>
+        <v>5779884.2599999998</v>
       </c>
       <c r="I33" s="155">
         <f t="shared" si="8"/>
-        <v>734780.88899999997</v>
+        <v>866982.63899999997</v>
       </c>
       <c r="J33" s="156">
         <f t="shared" si="0"/>
@@ -4228,22 +4209,22 @@
       </c>
       <c r="K33" s="156">
         <f t="shared" si="1"/>
-        <v>146563.58064999999</v>
+        <v>71149.866859999995</v>
       </c>
       <c r="L33" s="157">
         <v>0</v>
       </c>
       <c r="M33" s="158">
         <f t="shared" si="2"/>
-        <v>5779884.2599999998</v>
+        <v>6718017.2599999998</v>
       </c>
       <c r="N33" s="159">
         <f t="shared" si="3"/>
-        <v>6126677.2599999998</v>
+        <v>7121098.2599999998</v>
       </c>
       <c r="O33" s="160">
         <f t="shared" si="4"/>
-        <v>5953281.2599999998</v>
+        <v>6919558.2599999998</v>
       </c>
       <c r="P33" s="129">
         <f t="shared" si="6"/>
@@ -4251,7 +4232,7 @@
       </c>
       <c r="Q33" s="130"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
@@ -4271,7 +4252,7 @@
       <c r="O34" s="85"/>
       <c r="P34" s="51"/>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="88"/>
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
@@ -4281,15 +4262,15 @@
       </c>
       <c r="F35" s="61">
         <f>SUM(F8:F34)</f>
-        <v>28481663.509999998</v>
+        <v>33979187.509999998</v>
       </c>
       <c r="G35" s="66">
         <f>SUM(G8:G34)</f>
-        <v>1111121.19</v>
+        <v>1649630.34</v>
       </c>
       <c r="H35" s="66">
         <f>SUM(H8:H33)</f>
-        <v>27185297.859999992</v>
+        <v>32062859.709999993</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -4298,7 +4279,7 @@
       </c>
       <c r="K35" s="61">
         <f t="shared" si="10"/>
-        <v>2402681.6499999994</v>
+        <v>1166391.26</v>
       </c>
       <c r="L35" s="66">
         <f t="shared" si="10"/>
@@ -4306,113 +4287,104 @@
       </c>
       <c r="M35" s="91">
         <f t="shared" si="10"/>
-        <v>33952743.509999998</v>
+        <v>38295222.509999998</v>
       </c>
       <c r="N35" s="91">
         <f t="shared" si="10"/>
-        <v>35989913.509999998</v>
+        <v>40592938.509999998</v>
       </c>
       <c r="O35" s="91">
         <f t="shared" si="10"/>
-        <v>34696627.049999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39310726.049999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="207" t="s">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="191" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="207"/>
-      <c r="E38" s="207"/>
-      <c r="F38" s="207"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="207"/>
-      <c r="I38" s="207"/>
-      <c r="J38" s="207"/>
-      <c r="K38" s="207"/>
-      <c r="L38" s="207"/>
-      <c r="M38" s="207"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="207"/>
-      <c r="D39" s="207"/>
-      <c r="E39" s="207"/>
-      <c r="F39" s="207"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="207"/>
-      <c r="J39" s="207"/>
-      <c r="K39" s="207"/>
-      <c r="L39" s="207"/>
-      <c r="M39" s="207"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="207"/>
-      <c r="D40" s="207"/>
-      <c r="E40" s="207"/>
-      <c r="F40" s="207"/>
-      <c r="G40" s="207"/>
-      <c r="H40" s="207"/>
-      <c r="I40" s="207"/>
-      <c r="J40" s="207"/>
-      <c r="K40" s="207"/>
-      <c r="L40" s="207"/>
-      <c r="M40" s="207"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="207"/>
-      <c r="D41" s="207"/>
-      <c r="E41" s="207"/>
-      <c r="F41" s="207"/>
-      <c r="G41" s="207"/>
-      <c r="H41" s="207"/>
-      <c r="I41" s="207"/>
-      <c r="J41" s="207"/>
-      <c r="K41" s="207"/>
-      <c r="L41" s="207"/>
-      <c r="M41" s="207"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="207"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="207"/>
-      <c r="F42" s="207"/>
-      <c r="G42" s="207"/>
-      <c r="H42" s="207"/>
-      <c r="I42" s="207"/>
-      <c r="J42" s="207"/>
-      <c r="K42" s="207"/>
-      <c r="L42" s="207"/>
-      <c r="M42" s="207"/>
-    </row>
-    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="207"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
-      <c r="G43" s="207"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="207"/>
-      <c r="J43" s="207"/>
-      <c r="K43" s="207"/>
-      <c r="L43" s="207"/>
-      <c r="M43" s="207"/>
+      <c r="D38" s="191"/>
+      <c r="E38" s="191"/>
+      <c r="F38" s="191"/>
+      <c r="G38" s="191"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="191"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="191"/>
+      <c r="D39" s="191"/>
+      <c r="E39" s="191"/>
+      <c r="F39" s="191"/>
+      <c r="G39" s="191"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="191"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
+      <c r="G40" s="191"/>
+      <c r="H40" s="191"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191"/>
+      <c r="K40" s="191"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="191"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="191"/>
+      <c r="D41" s="191"/>
+      <c r="E41" s="191"/>
+      <c r="F41" s="191"/>
+      <c r="G41" s="191"/>
+      <c r="H41" s="191"/>
+      <c r="I41" s="191"/>
+      <c r="J41" s="191"/>
+      <c r="K41" s="191"/>
+      <c r="L41" s="191"/>
+      <c r="M41" s="191"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="191"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="191"/>
+      <c r="H42" s="191"/>
+      <c r="I42" s="191"/>
+      <c r="J42" s="191"/>
+      <c r="K42" s="191"/>
+      <c r="L42" s="191"/>
+      <c r="M42" s="191"/>
+    </row>
+    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="191"/>
+      <c r="D43" s="191"/>
+      <c r="E43" s="191"/>
+      <c r="F43" s="191"/>
+      <c r="G43" s="191"/>
+      <c r="H43" s="191"/>
+      <c r="I43" s="191"/>
+      <c r="J43" s="191"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4423,6 +4395,15 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4431,13 +4412,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A25B88-8B45-4057-AF50-E99CF1B30302}">
-  <dimension ref="C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C6:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="171" t="s">
-        <v>111</v>
-      </c>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="130"/>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="130"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
+++ b/2026/GALERIA/Septiembre/GALERIA Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9385459-5F95-471C-9F7F-3EBA01AE04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1E4D84-4AA2-4F2A-AE59-9EF8E1E6A6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="113">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -373,6 +368,9 @@
   </si>
   <si>
     <t>A la administracion se le debe en conepto de "deuda vieja" el monto especificado en el cartel de abajo - Por separado se adeudan honorarios del mes 7, 8 y 9 del 2026</t>
+  </si>
+  <si>
+    <t>UF 13  DEPOSITO $500.000 15/10</t>
   </si>
 </sst>
 </file>
@@ -568,7 +566,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +639,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="29">
     <border>
@@ -988,7 +992,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1284,12 +1288,48 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1320,42 +1360,8 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1434,9 +1440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1474,9 +1480,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1509,26 +1515,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1561,26 +1550,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1755,20 +1727,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="73" t="s">
         <v>84</v>
@@ -1777,7 +1749,7 @@
       <c r="D1" s="73"/>
       <c r="E1" s="74"/>
     </row>
-    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="75" t="s">
         <v>47</v>
@@ -1786,7 +1758,7 @@
       <c r="D2" s="75"/>
       <c r="E2" s="76"/>
     </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
       <c r="B3" s="93" t="s">
         <v>45</v>
@@ -1795,7 +1767,7 @@
       <c r="D3" s="93"/>
       <c r="E3" s="76"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1806,7 +1778,7 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>105</v>
       </c>
@@ -1815,7 +1787,7 @@
       <c r="D5" s="75"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>82</v>
       </c>
@@ -1824,22 +1796,22 @@
       <c r="D6" s="20"/>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="173" t="s">
         <v>104</v>
       </c>
       <c r="C8" s="173"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="173"/>
       <c r="C9" s="173"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="173"/>
       <c r="C10" s="173"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="181" t="s">
         <v>83</v>
       </c>
@@ -1848,33 +1820,33 @@
       <c r="D13" s="181"/>
       <c r="E13" s="181"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="181"/>
       <c r="B14" s="181"/>
       <c r="C14" s="181"/>
       <c r="D14" s="181"/>
       <c r="E14" s="181"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="181"/>
       <c r="B15" s="181"/>
       <c r="C15" s="181"/>
       <c r="D15" s="181"/>
       <c r="E15" s="181"/>
     </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="181"/>
       <c r="B16" s="181"/>
       <c r="C16" s="181"/>
       <c r="D16" s="181"/>
       <c r="E16" s="181"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1883,7 +1855,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>36</v>
       </c>
@@ -1893,7 +1865,7 @@
       <c r="E21" s="98"/>
       <c r="G21" s="22"/>
     </row>
-    <row r="22" spans="1:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="174" t="s">
         <v>110</v>
       </c>
@@ -1908,7 +1880,7 @@
       <c r="F22" s="48"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="174" t="s">
         <v>111</v>
       </c>
@@ -1919,7 +1891,7 @@
       <c r="F23" s="48"/>
       <c r="H23" s="22"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="29" t="s">
         <v>33</v>
       </c>
@@ -1931,7 +1903,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
         <v>49</v>
       </c>
@@ -1940,7 +1912,7 @@
       <c r="D25" s="134"/>
       <c r="E25" s="106"/>
     </row>
-    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="174" t="s">
         <v>97</v>
       </c>
@@ -1953,7 +1925,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="174" t="s">
         <v>106</v>
       </c>
@@ -1964,7 +1936,7 @@
       </c>
       <c r="E27" s="121"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
         <v>1</v>
       </c>
@@ -1977,7 +1949,7 @@
       </c>
       <c r="G28" s="151"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
         <v>35</v>
       </c>
@@ -1986,7 +1958,7 @@
       <c r="D29" s="43"/>
       <c r="E29" s="100"/>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>78</v>
       </c>
@@ -1995,7 +1967,7 @@
       <c r="D30" s="120"/>
       <c r="E30" s="104"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>77</v>
       </c>
@@ -2006,7 +1978,7 @@
       </c>
       <c r="E31" s="121"/>
     </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>77</v>
       </c>
@@ -2015,7 +1987,7 @@
       <c r="D32" s="120"/>
       <c r="E32" s="104"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>77</v>
       </c>
@@ -2024,14 +1996,14 @@
       <c r="D33" s="120"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="120"/>
       <c r="E34" s="104"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
         <v>2</v>
       </c>
@@ -2043,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="38" t="s">
         <v>34</v>
       </c>
@@ -2052,7 +2024,7 @@
       <c r="D36" s="42"/>
       <c r="E36" s="102"/>
     </row>
-    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="170" t="s">
         <v>100</v>
       </c>
@@ -2064,7 +2036,7 @@
       <c r="E37" s="121"/>
       <c r="J37" s="60"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
         <v>7</v>
       </c>
@@ -2076,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="38" t="s">
         <v>26</v>
       </c>
@@ -2085,7 +2057,7 @@
       <c r="D39" s="31"/>
       <c r="E39" s="102"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -2096,7 +2068,7 @@
       </c>
       <c r="E40" s="107"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>102</v>
       </c>
@@ -2107,7 +2079,7 @@
       </c>
       <c r="E41" s="105"/>
     </row>
-    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="59" t="s">
         <v>33</v>
       </c>
@@ -2119,14 +2091,14 @@
         <v>117318.25</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="97"/>
       <c r="E43" s="109"/>
     </row>
-    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="32" t="s">
         <v>103</v>
       </c>
@@ -2137,13 +2109,13 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="D45" s="112"/>
       <c r="E45" s="113"/>
       <c r="F45" s="51"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>27</v>
       </c>
@@ -2156,15 +2128,15 @@
       </c>
       <c r="F46" s="51"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D47" s="112"/>
       <c r="E47" s="112"/>
     </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D48" s="112"/>
       <c r="E48" s="112"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>37</v>
       </c>
@@ -2173,35 +2145,35 @@
       <c r="D49" s="116"/>
       <c r="E49" s="117"/>
     </row>
-    <row r="50" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="174"/>
       <c r="B50" s="175"/>
       <c r="C50" s="5"/>
       <c r="D50" s="103"/>
       <c r="E50" s="101"/>
     </row>
-    <row r="51" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="174"/>
       <c r="B51" s="175"/>
       <c r="C51" s="5"/>
       <c r="D51" s="103"/>
       <c r="E51" s="101"/>
     </row>
-    <row r="52" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="179"/>
       <c r="B52" s="180"/>
       <c r="C52" s="5"/>
       <c r="D52" s="103"/>
       <c r="E52" s="101"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="122"/>
       <c r="B53" s="123"/>
       <c r="C53" s="60"/>
       <c r="D53" s="103"/>
       <c r="E53" s="101"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="57"/>
       <c r="B54" s="56"/>
       <c r="C54" s="56"/>
@@ -2211,9 +2183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="32" t="s">
         <v>38</v>
       </c>
@@ -2222,8 +2194,8 @@
       <c r="D57" s="33"/>
       <c r="E57" s="125"/>
     </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>39</v>
       </c>
@@ -2235,8 +2207,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="94" t="s">
         <v>28</v>
       </c>
@@ -2246,7 +2218,7 @@
       </c>
       <c r="D61" s="51"/>
     </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="94" t="s">
         <v>29</v>
       </c>
@@ -2255,7 +2227,7 @@
         <v>666391.26</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="94" t="s">
         <v>40</v>
       </c>
@@ -2264,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="94" t="s">
         <v>55</v>
       </c>
@@ -2273,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="178" t="s">
         <v>93</v>
       </c>
@@ -2282,22 +2254,22 @@
       <c r="D67" s="178"/>
       <c r="E67" s="178"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="178"/>
       <c r="B68" s="178"/>
       <c r="C68" s="178"/>
       <c r="D68" s="178"/>
       <c r="E68" s="178"/>
     </row>
-    <row r="69" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="178"/>
       <c r="B69" s="178"/>
       <c r="C69" s="178"/>
       <c r="D69" s="178"/>
       <c r="E69" s="178"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="182" t="s">
         <v>109</v>
       </c>
@@ -2306,35 +2278,35 @@
       <c r="D71" s="183"/>
       <c r="E71" s="184"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="185"/>
       <c r="B72" s="186"/>
       <c r="C72" s="186"/>
       <c r="D72" s="186"/>
       <c r="E72" s="187"/>
     </row>
-    <row r="73" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="188"/>
       <c r="B73" s="189"/>
       <c r="C73" s="189"/>
       <c r="D73" s="189"/>
       <c r="E73" s="190"/>
     </row>
-    <row r="74" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="163"/>
       <c r="B74" s="163"/>
       <c r="C74" s="163"/>
       <c r="D74" s="163"/>
       <c r="E74" s="163"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="165" t="s">
         <v>51</v>
       </c>
       <c r="B75" s="166"/>
       <c r="C75" s="23"/>
     </row>
-    <row r="76" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="167" t="s">
         <v>90</v>
       </c>
@@ -2343,7 +2315,7 @@
       </c>
       <c r="C76" s="25"/>
     </row>
-    <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>57</v>
       </c>
@@ -2353,14 +2325,14 @@
       </c>
       <c r="C77" s="23"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
         <v>58</v>
       </c>
       <c r="B78" s="47"/>
       <c r="C78" s="23"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
         <v>86</v>
       </c>
@@ -2370,7 +2342,7 @@
       </c>
       <c r="C79" s="23"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="s">
         <v>98</v>
       </c>
@@ -2379,7 +2351,7 @@
       </c>
       <c r="C80" s="23"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="46" t="s">
         <v>41</v>
       </c>
@@ -2389,7 +2361,7 @@
       </c>
       <c r="C81" s="23"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="27" t="s">
         <v>42</v>
       </c>
@@ -2399,7 +2371,7 @@
       </c>
       <c r="C82" s="23"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="34" t="s">
         <v>33</v>
       </c>
@@ -2412,21 +2384,21 @@
       <c r="E83" s="151"/>
       <c r="F83" s="151"/>
     </row>
-    <row r="84" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="48"/>
       <c r="C84" s="26"/>
       <c r="D84" s="51"/>
     </row>
-    <row r="85" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="49"/>
       <c r="C85" s="26"/>
     </row>
-    <row r="86" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86"/>
       <c r="B86" s="48"/>
       <c r="C86" s="44"/>
     </row>
-    <row r="87" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="35" t="s">
         <v>31</v>
       </c>
@@ -2434,7 +2406,7 @@
       <c r="C87" s="44"/>
       <c r="D87" s="54"/>
     </row>
-    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>30</v>
       </c>
@@ -2443,7 +2415,7 @@
       </c>
       <c r="C88" s="44"/>
     </row>
-    <row r="89" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>23</v>
       </c>
@@ -2453,7 +2425,7 @@
       <c r="C89" s="26"/>
       <c r="D89" s="51"/>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>41</v>
       </c>
@@ -2462,7 +2434,7 @@
       </c>
       <c r="C90" s="26"/>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>42</v>
       </c>
@@ -2471,7 +2443,7 @@
       </c>
       <c r="C91" s="28"/>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="35" t="s">
         <v>32</v>
       </c>
@@ -2481,28 +2453,28 @@
       </c>
       <c r="C92" s="23"/>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="177" t="s">
         <v>50</v>
       </c>
       <c r="B95" s="177"/>
       <c r="C95" s="177"/>
     </row>
-    <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="177"/>
       <c r="B96" s="177"/>
       <c r="C96" s="177"/>
     </row>
-    <row r="97" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="118"/>
       <c r="B97" s="40"/>
       <c r="C97" s="164">
         <v>40000</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="52" t="s">
         <v>7</v>
       </c>
@@ -2512,31 +2484,31 @@
       </c>
       <c r="C98" s="53"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M99" s="8"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="176"/>
       <c r="B100" s="176"/>
       <c r="C100" s="176"/>
       <c r="D100" s="176"/>
       <c r="E100" s="176"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="176"/>
       <c r="B101" s="176"/>
       <c r="C101" s="176"/>
       <c r="D101" s="176"/>
       <c r="E101" s="176"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="176"/>
       <c r="B102" s="176"/>
       <c r="C102" s="176"/>
       <c r="D102" s="176"/>
       <c r="E102" s="176"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="176"/>
       <c r="B103" s="176"/>
       <c r="C103" s="176"/>
@@ -2568,36 +2540,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="204" t="s">
+      <c r="C1" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2609,13 +2581,13 @@
       <c r="O1" s="62"/>
       <c r="P1" s="22"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="192"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2627,13 +2599,13 @@
       <c r="O2" s="62"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="205"/>
-      <c r="D3" s="205"/>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2641,11 +2613,11 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="206">
+      <c r="L3" s="193">
         <f>Q3</f>
         <v>1166391.26</v>
       </c>
-      <c r="M3" s="206"/>
+      <c r="M3" s="193"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
@@ -2653,13 +2625,13 @@
         <v>1166391.26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2667,99 +2639,99 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="207"/>
-      <c r="M4" s="207"/>
+      <c r="L4" s="194"/>
+      <c r="M4" s="194"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
-    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="210" t="s">
+    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="199" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="211"/>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="212"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="208" t="s">
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
+      <c r="M5" s="200"/>
+      <c r="N5" s="200"/>
+      <c r="O5" s="201"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="195" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="192" t="s">
+      <c r="C6" s="197" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="192" t="s">
+      <c r="D6" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="192" t="s">
+      <c r="E6" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="192" t="s">
+      <c r="F6" s="197" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="192" t="s">
+      <c r="G6" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="201" t="s">
+      <c r="H6" s="213" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="201" t="s">
+      <c r="I6" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="196" t="s">
+      <c r="J6" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="196" t="s">
+      <c r="K6" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="199" t="s">
+      <c r="L6" s="211" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="194" t="s">
+      <c r="N6" s="206" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="213" t="s">
+      <c r="O6" s="202" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="209"/>
-      <c r="B7" s="203"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="202"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="200"/>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="196"/>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="198"/>
+      <c r="H7" s="214"/>
+      <c r="I7" s="214"/>
+      <c r="J7" s="209"/>
+      <c r="K7" s="210"/>
+      <c r="L7" s="212"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="N7" s="195"/>
-      <c r="O7" s="214"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="207"/>
+      <c r="O7" s="203"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2814,7 +2786,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="60" t="s">
         <v>9</v>
       </c>
@@ -2875,7 +2847,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
         <v>9</v>
       </c>
@@ -2932,7 +2904,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -2992,7 +2964,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -3048,7 +3020,7 @@
       </c>
       <c r="R12" s="51"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3109,7 +3081,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -3166,7 +3138,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3223,7 +3195,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
@@ -3280,7 +3252,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -3333,7 +3305,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -3386,7 +3358,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="60" t="s">
         <v>14</v>
       </c>
@@ -3441,15 +3413,15 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="68">
+      <c r="B20" s="215">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="215" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="86"/>
@@ -3501,7 +3473,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
@@ -3561,7 +3533,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
@@ -3616,7 +3588,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
@@ -3672,7 +3644,7 @@
       </c>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="60" t="s">
         <v>16</v>
       </c>
@@ -3727,7 +3699,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="60" t="s">
         <v>17</v>
       </c>
@@ -3785,7 +3757,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="60" t="s">
         <v>17</v>
       </c>
@@ -3840,7 +3812,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="60" t="s">
         <v>18</v>
       </c>
@@ -3895,7 +3867,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="60" t="s">
         <v>19</v>
       </c>
@@ -3952,7 +3924,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="60" t="s">
         <v>20</v>
       </c>
@@ -4009,7 +3981,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>21</v>
       </c>
@@ -4064,7 +4036,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
@@ -4121,7 +4093,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>24</v>
       </c>
@@ -4174,7 +4146,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -4232,7 +4204,7 @@
       </c>
       <c r="Q33" s="130"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
@@ -4252,7 +4224,7 @@
       <c r="O34" s="85"/>
       <c r="P34" s="51"/>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="88"/>
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
@@ -4298,93 +4270,102 @@
         <v>39310726.049999997</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="191" t="s">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="204" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="191"/>
-      <c r="E38" s="191"/>
-      <c r="F38" s="191"/>
-      <c r="G38" s="191"/>
-      <c r="H38" s="191"/>
-      <c r="I38" s="191"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="191"/>
-      <c r="M38" s="191"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="191"/>
-      <c r="D39" s="191"/>
-      <c r="E39" s="191"/>
-      <c r="F39" s="191"/>
-      <c r="G39" s="191"/>
-      <c r="H39" s="191"/>
-      <c r="I39" s="191"/>
-      <c r="J39" s="191"/>
-      <c r="K39" s="191"/>
-      <c r="L39" s="191"/>
-      <c r="M39" s="191"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="191"/>
-      <c r="D40" s="191"/>
-      <c r="E40" s="191"/>
-      <c r="F40" s="191"/>
-      <c r="G40" s="191"/>
-      <c r="H40" s="191"/>
-      <c r="I40" s="191"/>
-      <c r="J40" s="191"/>
-      <c r="K40" s="191"/>
-      <c r="L40" s="191"/>
-      <c r="M40" s="191"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="191"/>
-      <c r="D41" s="191"/>
-      <c r="E41" s="191"/>
-      <c r="F41" s="191"/>
-      <c r="G41" s="191"/>
-      <c r="H41" s="191"/>
-      <c r="I41" s="191"/>
-      <c r="J41" s="191"/>
-      <c r="K41" s="191"/>
-      <c r="L41" s="191"/>
-      <c r="M41" s="191"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="191"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="191"/>
-      <c r="F42" s="191"/>
-      <c r="G42" s="191"/>
-      <c r="H42" s="191"/>
-      <c r="I42" s="191"/>
-      <c r="J42" s="191"/>
-      <c r="K42" s="191"/>
-      <c r="L42" s="191"/>
-      <c r="M42" s="191"/>
-    </row>
-    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="191"/>
-      <c r="D43" s="191"/>
-      <c r="E43" s="191"/>
-      <c r="F43" s="191"/>
-      <c r="G43" s="191"/>
-      <c r="H43" s="191"/>
-      <c r="I43" s="191"/>
-      <c r="J43" s="191"/>
-      <c r="K43" s="191"/>
-      <c r="L43" s="191"/>
-      <c r="M43" s="191"/>
+      <c r="D38" s="204"/>
+      <c r="E38" s="204"/>
+      <c r="F38" s="204"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="204"/>
+      <c r="I38" s="204"/>
+      <c r="J38" s="204"/>
+      <c r="K38" s="204"/>
+      <c r="L38" s="204"/>
+      <c r="M38" s="204"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="204"/>
+      <c r="D39" s="204"/>
+      <c r="E39" s="204"/>
+      <c r="F39" s="204"/>
+      <c r="G39" s="204"/>
+      <c r="H39" s="204"/>
+      <c r="I39" s="204"/>
+      <c r="J39" s="204"/>
+      <c r="K39" s="204"/>
+      <c r="L39" s="204"/>
+      <c r="M39" s="204"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="204"/>
+      <c r="D40" s="204"/>
+      <c r="E40" s="204"/>
+      <c r="F40" s="204"/>
+      <c r="G40" s="204"/>
+      <c r="H40" s="204"/>
+      <c r="I40" s="204"/>
+      <c r="J40" s="204"/>
+      <c r="K40" s="204"/>
+      <c r="L40" s="204"/>
+      <c r="M40" s="204"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="204"/>
+      <c r="D41" s="204"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="204"/>
+      <c r="G41" s="204"/>
+      <c r="H41" s="204"/>
+      <c r="I41" s="204"/>
+      <c r="J41" s="204"/>
+      <c r="K41" s="204"/>
+      <c r="L41" s="204"/>
+      <c r="M41" s="204"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="204"/>
+      <c r="D42" s="204"/>
+      <c r="E42" s="204"/>
+      <c r="F42" s="204"/>
+      <c r="G42" s="204"/>
+      <c r="H42" s="204"/>
+      <c r="I42" s="204"/>
+      <c r="J42" s="204"/>
+      <c r="K42" s="204"/>
+      <c r="L42" s="204"/>
+      <c r="M42" s="204"/>
+    </row>
+    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="204"/>
+      <c r="D43" s="204"/>
+      <c r="E43" s="204"/>
+      <c r="F43" s="204"/>
+      <c r="G43" s="204"/>
+      <c r="H43" s="204"/>
+      <c r="I43" s="204"/>
+      <c r="J43" s="204"/>
+      <c r="K43" s="204"/>
+      <c r="L43" s="204"/>
+      <c r="M43" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4395,15 +4376,6 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4412,13 +4384,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A25B88-8B45-4057-AF50-E99CF1B30302}">
-  <dimension ref="C6:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B4:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="216" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C6" s="130"/>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C7" s="130"/>
     </row>
   </sheetData>
